--- a/Database/listen_data/Dapan_Listenning.xlsx
+++ b/Database/listen_data/Dapan_Listenning.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bun\KLTN_main\Database\listen_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bun\KLTN_final\KLTN\Database\listen_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E0B2D7-E2FD-49EF-8EE6-52CBA8569C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C68A0D-7A1A-4DB2-BC74-C4C3D4327A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9FCAEB9B-8E23-41D0-A159-BE22BE3F8954}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="278">
   <si>
     <t>AudioFile</t>
   </si>
@@ -1739,6 +1739,9 @@
 (A) Production costs are high. 
 (B) There was only one item on the agenda. 
 (C) No, we were the first to arrive. </t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -2188,9 +2191,6 @@
       <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
@@ -2217,9 +2217,6 @@
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
@@ -2239,15 +2236,11 @@
         <v xml:space="preserve">(B) No, thank you. 
 </v>
       </c>
-      <c r="E5" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>(C) Near the front entrance.</v>
+      <c r="E5" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.25">
@@ -2275,9 +2268,6 @@
       <c r="F6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="7" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
@@ -2304,9 +2294,6 @@
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
@@ -2333,9 +2320,6 @@
       <c r="F8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
@@ -2362,9 +2346,6 @@
       <c r="F9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="10" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
@@ -2391,9 +2372,6 @@
       <c r="F10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="11" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
@@ -2420,9 +2398,6 @@
       <c r="F11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="12" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
@@ -2449,9 +2424,6 @@
       <c r="F12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="13" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
@@ -2478,9 +2450,6 @@
       <c r="F13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
@@ -2507,9 +2476,6 @@
       <c r="F14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
@@ -2536,9 +2502,6 @@
       <c r="F15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="16" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
@@ -2565,11 +2528,8 @@
       <c r="F16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q16.mp3</v>
@@ -2594,11 +2554,8 @@
       <c r="F17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q17.mp3</v>
@@ -2624,11 +2581,8 @@
       <c r="F18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q18.mp3</v>
@@ -2653,11 +2607,8 @@
       <c r="F19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q19.mp3</v>
@@ -2682,11 +2633,8 @@
       <c r="F20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q20.mp3</v>
@@ -2711,11 +2659,8 @@
       <c r="F21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q21.mp3</v>
@@ -2740,11 +2685,8 @@
       <c r="F22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q22.mp3</v>
@@ -2769,11 +2711,8 @@
       <c r="F23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q23.mp3</v>
@@ -2798,11 +2737,8 @@
       <c r="F24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
         <f t="shared" si="3"/>
         <v>Test1_Part2_Q24.mp3</v>
@@ -2827,11 +2763,8 @@
       <c r="F25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
@@ -2855,11 +2788,8 @@
       <c r="F26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>"Test2_Part2_Q" &amp; ROW(A2) &amp; ".mp3"</f>
         <v>Test2_Part2_Q2.mp3</v>
@@ -2884,11 +2814,8 @@
       <c r="F27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f t="shared" ref="A28:A49" si="4">"Test2_Part2_Q" &amp; ROW(A3) &amp; ".mp3"</f>
         <v>Test2_Part2_Q3.mp3</v>
@@ -2913,11 +2840,8 @@
       <c r="F28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G28" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q4.mp3</v>
@@ -2942,11 +2866,8 @@
       <c r="F29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q5.mp3</v>
@@ -2971,11 +2892,8 @@
       <c r="F30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q6.mp3</v>
@@ -3000,11 +2918,8 @@
       <c r="F31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q7.mp3</v>
@@ -3029,11 +2944,8 @@
       <c r="F32" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q8.mp3</v>
@@ -3058,11 +2970,8 @@
       <c r="F33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q9.mp3</v>
@@ -3087,11 +2996,8 @@
       <c r="F34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q10.mp3</v>
@@ -3116,11 +3022,8 @@
       <c r="F35" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q11.mp3</v>
@@ -3145,11 +3048,8 @@
       <c r="F36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q12.mp3</v>
@@ -3174,11 +3074,8 @@
       <c r="F37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q13.mp3</v>
@@ -3203,11 +3100,8 @@
       <c r="F38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q14.mp3</v>
@@ -3232,11 +3126,8 @@
       <c r="F39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q15.mp3</v>
@@ -3261,11 +3152,8 @@
       <c r="F40" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q16.mp3</v>
@@ -3290,11 +3178,8 @@
       <c r="F41" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q17.mp3</v>
@@ -3319,11 +3204,8 @@
       <c r="F42" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q18.mp3</v>
@@ -3348,11 +3230,8 @@
       <c r="F43" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q19.mp3</v>
@@ -3377,11 +3256,8 @@
       <c r="F44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f>"Test2_Part2_Q" &amp; ROW(A20) &amp; ".mp3"</f>
         <v>Test2_Part2_Q20.mp3</v>
@@ -3406,11 +3282,8 @@
       <c r="F45" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q21.mp3</v>
@@ -3435,11 +3308,8 @@
       <c r="F46" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q22.mp3</v>
@@ -3464,11 +3334,8 @@
       <c r="F47" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q23.mp3</v>
@@ -3493,11 +3360,8 @@
       <c r="F48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G48" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Test2_Part2_Q24.mp3</v>
@@ -3522,11 +3386,8 @@
       <c r="F49" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
         <f>"Test2_Part2_Q" &amp; ROW(A25) &amp; ".mp3"</f>
         <v>Test2_Part2_Q25.mp3</v>
@@ -3551,11 +3412,8 @@
       <c r="F50" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>61</v>
       </c>
@@ -3579,11 +3437,8 @@
       <c r="F51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G51" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
@@ -3607,11 +3462,8 @@
       <c r="F52" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G52" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
@@ -3635,11 +3487,8 @@
       <c r="F53" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G53" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
@@ -3663,11 +3512,8 @@
       <c r="F54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -3691,11 +3537,8 @@
       <c r="F55" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G55" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
@@ -3719,11 +3562,8 @@
       <c r="F56" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G56" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>70</v>
       </c>
@@ -3747,11 +3587,8 @@
       <c r="F57" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G57" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>71</v>
       </c>
@@ -3775,11 +3612,8 @@
       <c r="F58" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G58" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>72</v>
       </c>
@@ -3803,11 +3637,8 @@
       <c r="F59" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G59" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>73</v>
       </c>
@@ -3832,11 +3663,8 @@
       <c r="F60" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G60" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>74</v>
       </c>
@@ -3860,11 +3688,8 @@
       <c r="F61" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G61" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>75</v>
       </c>
@@ -3888,11 +3713,8 @@
       <c r="F62" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G62" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,11 +3738,8 @@
       <c r="F63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G63" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>77</v>
       </c>
@@ -3944,11 +3763,8 @@
       <c r="F64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G64" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>78</v>
       </c>
@@ -3972,11 +3788,8 @@
       <c r="F65" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
@@ -4000,11 +3813,8 @@
       <c r="F66" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>80</v>
       </c>
@@ -4028,11 +3838,8 @@
       <c r="F67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G67" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>95</v>
       </c>
@@ -4056,11 +3863,8 @@
       <c r="F68" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G68" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="str">
         <f>"Test4_Part2_Q" &amp; ROW(A2) &amp; ".mp3"</f>
         <v>Test4_Part2_Q2.mp3</v>
@@ -4085,11 +3889,8 @@
       <c r="F69" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G69" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="str">
         <f t="shared" ref="A70:A91" si="5">"Test4_Part2_Q" &amp; ROW(A3) &amp; ".mp3"</f>
         <v>Test4_Part2_Q3.mp3</v>
@@ -4114,11 +3915,8 @@
       <c r="F70" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G70" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q4.mp3</v>
@@ -4143,11 +3941,8 @@
       <c r="F71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G71" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q5.mp3</v>
@@ -4172,11 +3967,8 @@
       <c r="F72" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G72" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q6.mp3</v>
@@ -4201,11 +3993,8 @@
       <c r="F73" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G73" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q7.mp3</v>
@@ -4230,11 +4019,8 @@
       <c r="F74" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G74" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q8.mp3</v>
@@ -4259,11 +4045,8 @@
       <c r="F75" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G75" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q9.mp3</v>
@@ -4288,11 +4071,8 @@
       <c r="F76" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G76" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q10.mp3</v>
@@ -4317,11 +4097,8 @@
       <c r="F77" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G77" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="str">
         <f>"Test4_Part2_Q" &amp; ROW(A11) &amp; ".mp3"</f>
         <v>Test4_Part2_Q11.mp3</v>
@@ -4346,11 +4123,8 @@
       <c r="F78" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G78" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q12.mp3</v>
@@ -4375,11 +4149,8 @@
       <c r="F79" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G79" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q13.mp3</v>
@@ -4405,11 +4176,8 @@
       <c r="F80" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G80" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q14.mp3</v>
@@ -4434,11 +4202,8 @@
       <c r="F81" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G81" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q15.mp3</v>
@@ -4463,11 +4228,8 @@
       <c r="F82" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q16.mp3</v>
@@ -4492,11 +4254,8 @@
       <c r="F83" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G83" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q17.mp3</v>
@@ -4521,11 +4280,8 @@
       <c r="F84" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G84" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q18.mp3</v>
@@ -4551,11 +4307,8 @@
       <c r="F85" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G85" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q19.mp3</v>
@@ -4580,11 +4333,8 @@
       <c r="F86" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G86" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="str">
         <f>"Test4_Part2_Q" &amp; ROW(A20) &amp; ".mp3"</f>
         <v>Test4_Part2_Q20.mp3</v>
@@ -4609,11 +4359,8 @@
       <c r="F87" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G87" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q21.mp3</v>
@@ -4638,11 +4385,8 @@
       <c r="F88" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G88" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q22.mp3</v>
@@ -4667,11 +4411,8 @@
       <c r="F89" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G89" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q23.mp3</v>
@@ -4697,11 +4438,8 @@
       <c r="F90" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G90" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="str">
         <f t="shared" si="5"/>
         <v>Test4_Part2_Q24.mp3</v>
@@ -4726,11 +4464,8 @@
       <c r="F91" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G91" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="str">
         <f>"Test4_Part2_Q" &amp; ROW(A25) &amp; ".mp3"</f>
         <v>Test4_Part2_Q25.mp3</v>
@@ -4755,11 +4490,8 @@
       <c r="F92" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G92" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>121</v>
       </c>
@@ -4783,11 +4515,8 @@
       <c r="F93" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G93" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
         <f>"Test5_Part2_Q" &amp; ROW(A2) &amp; ".mp3"</f>
         <v>Test5_Part2_Q2.mp3</v>
@@ -4812,11 +4541,8 @@
       <c r="F94" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G94" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="str">
         <f t="shared" ref="A95:A116" si="6">"Test5_Part2_Q" &amp; ROW(A3) &amp; ".mp3"</f>
         <v>Test5_Part2_Q3.mp3</v>
@@ -4841,11 +4567,8 @@
       <c r="F95" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G95" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q4.mp3</v>
@@ -4870,11 +4593,8 @@
       <c r="F96" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G96" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q5.mp3</v>
@@ -4899,11 +4619,8 @@
       <c r="F97" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G97" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q6.mp3</v>
@@ -4928,11 +4645,8 @@
       <c r="F98" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G98" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q7.mp3</v>
@@ -4957,11 +4671,8 @@
       <c r="F99" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G99" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q8.mp3</v>
@@ -4986,11 +4697,8 @@
       <c r="F100" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G100" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q9.mp3</v>
@@ -5015,11 +4723,8 @@
       <c r="F101" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G101" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q10.mp3</v>
@@ -5044,11 +4749,8 @@
       <c r="F102" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G102" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q11.mp3</v>
@@ -5073,11 +4775,8 @@
       <c r="F103" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G103" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q12.mp3</v>
@@ -5102,11 +4801,8 @@
       <c r="F104" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G104" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q13.mp3</v>
@@ -5131,11 +4827,8 @@
       <c r="F105" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G105" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q14.mp3</v>
@@ -5160,11 +4853,8 @@
       <c r="F106" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G106" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q15.mp3</v>
@@ -5189,11 +4879,8 @@
       <c r="F107" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G107" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q16.mp3</v>
@@ -5218,11 +4905,8 @@
       <c r="F108" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G108" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q17.mp3</v>
@@ -5247,11 +4931,8 @@
       <c r="F109" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G109" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q18.mp3</v>
@@ -5276,11 +4957,8 @@
       <c r="F110" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G110" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q19.mp3</v>
@@ -5305,11 +4983,8 @@
       <c r="F111" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G111" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q20.mp3</v>
@@ -5334,11 +5009,8 @@
       <c r="F112" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G112" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="str">
         <f>"Test5_Part2_Q" &amp; ROW(A21) &amp; ".mp3"</f>
         <v>Test5_Part2_Q21.mp3</v>
@@ -5363,11 +5035,8 @@
       <c r="F113" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G113" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q22.mp3</v>
@@ -5392,11 +5061,8 @@
       <c r="F114" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G114" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q23.mp3</v>
@@ -5421,11 +5087,8 @@
       <c r="F115" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G115" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
         <f t="shared" si="6"/>
         <v>Test5_Part2_Q24.mp3</v>
@@ -5450,11 +5113,8 @@
       <c r="F116" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G116" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
         <f>"Test5_Part2_Q" &amp; ROW(A25) &amp; ".mp3"</f>
         <v>Test5_Part2_Q25.mp3</v>
@@ -5479,11 +5139,8 @@
       <c r="F117" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G117" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>147</v>
       </c>
@@ -5508,7 +5165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="str">
         <f>"Test6_Part2_Q" &amp; ROW(A2) &amp; ".mp3"</f>
         <v>Test6_Part2_Q2.mp3</v>
@@ -5534,7 +5191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f t="shared" ref="A120:A142" si="7">"Test6_Part2_Q" &amp; ROW(A3) &amp; ".mp3"</f>
         <v>Test6_Part2_Q3.mp3</v>
@@ -5560,7 +5217,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q4.mp3</v>
@@ -5586,7 +5243,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q5.mp3</v>
@@ -5612,7 +5269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q6.mp3</v>
@@ -5638,7 +5295,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q7.mp3</v>
@@ -5664,7 +5321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q8.mp3</v>
@@ -5690,7 +5347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q9.mp3</v>
@@ -5716,7 +5373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q10.mp3</v>
@@ -5742,7 +5399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="str">
         <f t="shared" si="7"/>
         <v>Test6_Part2_Q11.mp3</v>
